--- a/RESULTS/tables/risk_decile_calibration_external_hybridxgbrf.xlsx
+++ b/RESULTS/tables/risk_decile_calibration_external_hybridxgbrf.xlsx
@@ -470,22 +470,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02009079551887234</v>
+        <v>0.02040940959658324</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0112540192926045</v>
+        <v>0.01123595505617977</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01008710078895092</v>
+        <v>0.009936193935573101</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02725435793399811</v>
+        <v>0.02728966996073723</v>
       </c>
     </row>
     <row r="3">
@@ -493,22 +493,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03276232365890139</v>
+        <v>0.03441838653767167</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01607717041800643</v>
+        <v>0.01449275362318841</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0272937398403883</v>
+        <v>0.0274602472782135</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03840801492333412</v>
+        <v>0.04113876074552536</v>
       </c>
     </row>
     <row r="4">
@@ -516,22 +516,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04707357929884524</v>
+        <v>0.04965550983713946</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02737520128824477</v>
+        <v>0.03858520900321544</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03841769322752953</v>
+        <v>0.04114153608679771</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05902722850441933</v>
+        <v>0.05686118081212044</v>
       </c>
     </row>
     <row r="5">
@@ -539,22 +539,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C5" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D5" t="n">
-        <v>0.09055682417855769</v>
+        <v>0.06877423112615103</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1028938906752412</v>
+        <v>0.07407407407407407</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05911316350102425</v>
+        <v>0.05689482763409615</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1199108734726906</v>
+        <v>0.08497396111488342</v>
       </c>
     </row>
     <row r="6">
@@ -562,22 +562,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C6" t="n">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1357146553957883</v>
+        <v>0.1173494351778821</v>
       </c>
       <c r="E6" t="n">
-        <v>0.157051282051282</v>
+        <v>0.1239935587761675</v>
       </c>
       <c r="F6" t="n">
-        <v>0.119928240776062</v>
+        <v>0.08519753813743591</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1547512114048004</v>
+        <v>0.1560381650924683</v>
       </c>
     </row>
     <row r="7">
@@ -591,16 +591,16 @@
         <v>123</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1859298358967833</v>
+        <v>0.1859490831661071</v>
       </c>
       <c r="E7" t="n">
         <v>0.1977491961414791</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1547847986221313</v>
+        <v>0.1561126112937927</v>
       </c>
       <c r="G7" t="n">
-        <v>0.223862886428833</v>
+        <v>0.2131125777959824</v>
       </c>
     </row>
     <row r="8">
@@ -608,22 +608,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C8" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2685124444922969</v>
+        <v>0.2481600709631439</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2961165048543689</v>
+        <v>0.3027375201288245</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2238998413085938</v>
+        <v>0.2132917642593384</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3116123080253601</v>
+        <v>0.286172479391098</v>
       </c>
     </row>
     <row r="9">
@@ -634,19 +634,19 @@
         <v>623</v>
       </c>
       <c r="C9" t="n">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3693221283188601</v>
+        <v>0.3671675798502627</v>
       </c>
       <c r="E9" t="n">
-        <v>0.434991974317817</v>
+        <v>0.4141252006420545</v>
       </c>
       <c r="F9" t="n">
-        <v>0.311716765165329</v>
+        <v>0.2862406969070435</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4273278415203094</v>
+        <v>0.4784361124038696</v>
       </c>
     </row>
     <row r="10">
@@ -654,22 +654,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C10" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5373827327773502</v>
+        <v>0.608246857168213</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7331189710610932</v>
+        <v>0.7435483870967742</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4273851811885834</v>
+        <v>0.4791860580444336</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6720984578132629</v>
+        <v>0.7400417923927307</v>
       </c>
     </row>
     <row r="11">
@@ -677,22 +677,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C11" t="n">
-        <v>552</v>
+        <v>588</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7888277983473193</v>
+        <v>0.8398863424058896</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8903225806451613</v>
+        <v>0.9453376205787781</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6725492477416992</v>
+        <v>0.7400867938995361</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9094045162200928</v>
+        <v>0.9268113970756531</v>
       </c>
     </row>
   </sheetData>

--- a/RESULTS/tables/risk_decile_calibration_external_hybridxgbrf.xlsx
+++ b/RESULTS/tables/risk_decile_calibration_external_hybridxgbrf.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,37 +417,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Decile</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Deaths</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Mean Predicted Risk</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Observed Risk</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Min Predicted Risk</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Max Predicted Risk</t>
         </is>
